--- a/panchang-data/Doha2026.xlsx
+++ b/panchang-data/Doha2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5384">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16177,6 +16177,9 @@
   </si>
   <si>
     <t>121°04'50.11</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16666,7 +16669,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16752,7 +16755,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>51</v>
@@ -16838,7 +16841,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16924,7 +16927,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>90</v>
@@ -17010,7 +17013,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17096,7 +17099,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>126</v>
@@ -17182,7 +17185,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>144</v>
@@ -17268,7 +17271,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17354,7 +17357,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>51</v>
@@ -17440,7 +17443,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17526,7 +17529,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>90</v>
@@ -17612,7 +17615,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17698,7 +17701,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>126</v>
@@ -17784,7 +17787,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>144</v>
@@ -17870,7 +17873,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -17956,7 +17959,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>51</v>
@@ -18042,7 +18045,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18128,7 +18131,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>90</v>
@@ -18214,7 +18217,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18300,7 +18303,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>126</v>
@@ -18386,7 +18389,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>144</v>
@@ -18472,7 +18475,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18558,7 +18561,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>51</v>
@@ -18644,7 +18647,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18730,7 +18733,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>90</v>
@@ -18816,7 +18819,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18902,7 +18905,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>126</v>
@@ -18988,7 +18991,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>144</v>
@@ -19074,7 +19077,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19160,7 +19163,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>51</v>
@@ -19246,7 +19249,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19332,7 +19335,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>89</v>
+        <v>558</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>90</v>
@@ -19418,7 +19421,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19504,7 +19507,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>126</v>
@@ -19590,7 +19593,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>144</v>
@@ -19676,7 +19679,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19762,7 +19765,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>51</v>
@@ -19848,7 +19851,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19934,7 +19937,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>90</v>
@@ -20020,7 +20023,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20106,7 +20109,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>126</v>
@@ -20192,7 +20195,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>144</v>
@@ -20278,7 +20281,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20364,7 +20367,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>51</v>
@@ -20450,7 +20453,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20536,7 +20539,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>90</v>
@@ -20622,7 +20625,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20708,7 +20711,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>126</v>
@@ -20794,7 +20797,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>144</v>
@@ -20880,7 +20883,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -20966,7 +20969,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>51</v>
@@ -21052,7 +21055,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21138,7 +21141,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>90</v>
@@ -21224,7 +21227,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21310,7 +21313,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>126</v>
@@ -21396,7 +21399,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>144</v>
@@ -21482,7 +21485,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21568,7 +21571,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>51</v>
@@ -21654,7 +21657,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21740,7 +21743,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>90</v>
@@ -21826,7 +21829,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21912,7 +21915,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>558</v>
+        <v>1002</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>126</v>
@@ -21998,7 +22001,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>144</v>
@@ -22084,7 +22087,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22170,7 +22173,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>51</v>
@@ -22256,7 +22259,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22342,7 +22345,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>90</v>
@@ -22428,7 +22431,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22514,7 +22517,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>126</v>
@@ -22600,7 +22603,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>144</v>
@@ -22686,7 +22689,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22772,7 +22775,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>51</v>
@@ -22858,7 +22861,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22944,7 +22947,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>90</v>
@@ -23030,7 +23033,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23116,7 +23119,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>126</v>
@@ -23202,7 +23205,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>144</v>
@@ -23288,7 +23291,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23374,7 +23377,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>51</v>
@@ -23460,7 +23463,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23546,7 +23549,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>90</v>
@@ -23632,7 +23635,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23718,7 +23721,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>126</v>
@@ -23804,7 +23807,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>144</v>
@@ -23890,7 +23893,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -23976,7 +23979,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>51</v>
@@ -24062,7 +24065,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24148,7 +24151,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>90</v>
@@ -24234,7 +24237,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24320,7 +24323,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>126</v>
@@ -24406,7 +24409,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1002</v>
+        <v>1428</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>144</v>
@@ -24492,7 +24495,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24578,7 +24581,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>51</v>
@@ -24664,7 +24667,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24750,7 +24753,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>90</v>
@@ -24836,7 +24839,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24922,7 +24925,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>126</v>
@@ -25008,7 +25011,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>144</v>
@@ -25094,7 +25097,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25180,7 +25183,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>51</v>
@@ -25266,7 +25269,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25352,7 +25355,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>90</v>
@@ -25438,7 +25441,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25524,7 +25527,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>126</v>
@@ -25610,7 +25613,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>144</v>
@@ -25696,7 +25699,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25782,7 +25785,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>51</v>
@@ -25868,7 +25871,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -25954,7 +25957,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>90</v>
@@ -26040,7 +26043,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26126,7 +26129,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>126</v>
@@ -26212,7 +26215,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>144</v>
@@ -26298,7 +26301,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26384,7 +26387,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>51</v>
@@ -26470,7 +26473,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26556,7 +26559,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>90</v>
@@ -26642,7 +26645,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26728,7 +26731,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>126</v>
@@ -26814,7 +26817,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>144</v>
@@ -26900,7 +26903,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -26986,7 +26989,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1428</v>
+        <v>1866</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>51</v>
@@ -27072,7 +27075,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1866</v>
+        <v>2302</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27158,7 +27161,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1866</v>
+        <v>2302</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>90</v>
@@ -27244,7 +27247,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1866</v>
+        <v>2302</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27330,7 +27333,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1866</v>
+        <v>2302</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>126</v>
@@ -27416,7 +27419,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1866</v>
+        <v>2302</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>144</v>
@@ -27502,7 +27505,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1866</v>
+        <v>2302</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27588,7 +27591,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1866</v>
+        <v>2302</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>51</v>
@@ -27674,7 +27677,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1866</v>
+        <v>2302</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27760,7 +27763,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1866</v>
+        <v>2302</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>90</v>
@@ -27846,7 +27849,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1866</v>
+        <v>2302</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27932,7 +27935,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1866</v>
+        <v>2302</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>126</v>
@@ -28018,7 +28021,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1866</v>
+        <v>2302</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>144</v>
@@ -28104,7 +28107,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1866</v>
+        <v>2302</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28190,7 +28193,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1866</v>
+        <v>2302</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>51</v>
@@ -28276,7 +28279,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1866</v>
+        <v>2302</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28362,7 +28365,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1866</v>
+        <v>5383</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>90</v>
@@ -28448,7 +28451,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1866</v>
+        <v>5383</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28534,7 +28537,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1866</v>
+        <v>5383</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>126</v>
@@ -28620,7 +28623,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1866</v>
+        <v>5383</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>144</v>
@@ -28706,7 +28709,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1866</v>
+        <v>5383</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28792,7 +28795,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1866</v>
+        <v>5383</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>51</v>
@@ -28878,7 +28881,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1866</v>
+        <v>5383</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -28964,7 +28967,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1866</v>
+        <v>5383</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>90</v>
@@ -29050,7 +29053,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1866</v>
+        <v>5383</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29136,7 +29139,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1866</v>
+        <v>5383</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>126</v>
@@ -29222,7 +29225,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1866</v>
+        <v>5383</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>144</v>
@@ -29308,7 +29311,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1866</v>
+        <v>5383</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29394,7 +29397,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1866</v>
+        <v>5383</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>51</v>
@@ -29480,7 +29483,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1866</v>
+        <v>5383</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29566,7 +29569,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1866</v>
+        <v>5383</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>90</v>
@@ -29652,7 +29655,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2302</v>
+        <v>5383</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29738,7 +29741,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2302</v>
+        <v>5383</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>126</v>
@@ -29824,7 +29827,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2302</v>
+        <v>5383</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>144</v>
@@ -29910,7 +29913,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2302</v>
+        <v>5383</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -29996,7 +29999,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2302</v>
+        <v>5383</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>51</v>
@@ -30082,7 +30085,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2302</v>
+        <v>5383</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30168,7 +30171,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2302</v>
+        <v>5383</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>90</v>
@@ -30254,7 +30257,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2302</v>
+        <v>5383</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30340,7 +30343,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2302</v>
+        <v>5383</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>126</v>
@@ -30426,7 +30429,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2302</v>
+        <v>5383</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>144</v>
@@ -30512,7 +30515,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2302</v>
+        <v>5383</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30598,7 +30601,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2302</v>
+        <v>5383</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>51</v>
@@ -30684,7 +30687,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2302</v>
+        <v>5383</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30770,7 +30773,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2302</v>
+        <v>5383</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>90</v>
@@ -30856,7 +30859,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2302</v>
+        <v>5383</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
